--- a/US_Colleges_Fall_2027_Full_Ride_BDtoUSA.xlsx
+++ b/US_Colleges_Fall_2027_Full_Ride_BDtoUSA.xlsx
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AP2" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: 'The absolute #1 target for high-need int'ls in ED1.' Shifted to need-blind for int'ls in 2022. Extremely friendly to South Asian STEM applicants. Packages are 100% pure grants with $0 loans and includes winter coat stipend and campus gear.</t>
+          <t>THE #1 ED1 NEED-BLIND TARGET (r/IntltoUSA Consensus): Shifted to need-blind for all international students in 2022. Bowdoin's financial aid packages are 100% pure grants with zero loans, and include health insurance, a campus technology stipend, and a winter coat allowance. Applying ED1 provides an enormous statistical boost. Accepts the free ISFAA PDF uploaded directly to the applicant portal, saving the CSS Profile fee.</t>
         </is>
       </c>
       <c r="AQ2" s="3" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AP3" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Part of the elite 9 need-blind universities. Brown and Notre Dame recently transitioned to international need-blind. Full rides cover 100% on I-20, guaranteeing effortless F-1 visa clearance at Dhaka Embassy.</t>
+          <t>ELITE NEED-BLIND POWERHOUSE (r/IntltoUSA Consensus): One of the foundational international need-blind colleges. Financial aid packages are all-grant (no loans) and cover 100% on Form I-20, guaranteeing rapid F-1 visa clearance at the Dhaka Embassy. Test-optional, but admitted South Asian students typically present stellar academic transcripts and strong personal statements.</t>
         </is>
       </c>
       <c r="AQ3" s="7" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: The legendary Need-Blind Holy Trinity. True $0 family contribution guaranteed. Princeton PFAA is 100% free. Admissions is holistic but requires world-class spike or national rank.</t>
+          <t>THE GOLD STANDARD OF FINANCIAL AID (r/IntltoUSA Consensus): Princeton guarantees $0 family contribution for families earning under $100,000. Uses its own free Princeton Financial Aid Application (PFAA), completely bypassing the CSS Profile fee. Evaluates applications 100% need-blind with an unmatched undergraduate focus and zero graduate student TAs.</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="AP5" s="7" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: 'Historic game-changer after the $132M gift—now one of only 10 true need-blind schools in the US for internationals, meeting 100% need with zero loans.'</t>
+          <t>HISTORIC NEED-BLIND GAME-CHANGER (r/IntltoUSA Consensus): Following a monumental $132M gift, W&amp;L joined the elite 10 need-blind universities for internationals, meeting 100% of need with zero loans. In addition, the Johnson Scholarship offers full ride merit awards plus $10,000 summer grants. Highly recommended for ED1/ED2.</t>
         </is>
       </c>
       <c r="AQ5" s="7" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: 'The single most generous undergraduate institution in existence.' Known as the legendary full ride portal. Provides round-trip annual airfare to Dhaka, on-campus health insurance, laptop, and personal monthly stipend. Extremely competitive, but Bangladeshis have a strong annual admit history.</t>
+          <t>THE MOST GENEROUS INSTITUTION GLOBALLY (r/IntltoUSA Consensus): Known across r/IntltoUSA as the ultimate full ride portal. NYUAD's package covers tuition, room, board, health insurance, annual round-trip flights to Dhaka, a brand new laptop, and a personal monthly stipend. ED1 yields the highest historical admit rate for Bangladeshi applicants; finalist invites to Candidate Weekend are required.</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AP7" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Technical Project Upload: Upload your research paper abstract or scientific manuscript and live GitHub repository links (web platforms, mobile apps, and technical repositories) directly to your application portal under 'Supplemental Research Materials'. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>ENDOWMENT GIANT ($2.5B+) (r/IntltoUSA Consensus): Grinnell possesses one of the highest per-student endowments in the nation. Historically admits high-need South Asians in ED with generous full rides. In Regular Decision, however, Grinnell aggressively manages yield and waitlists high-need applicants.</t>
         </is>
       </c>
       <c r="AQ7" s="7" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Davis AI Institute makes Colby the premier LAC for ML/deep learning. 3x-4x acceptance rate advantage in ED1. Zero application fee and free ISFAA makes it a staple for Bangladeshi applicants.</t>
+          <t>DAVIS AI HUB + FREE ISFAA (r/IntltoUSA Consensus): Colby offers zero application fees and accepts the free ISFAA PDF uploaded to the portal. Home to the Davis Institute for Artificial Intelligence. Community reality: Colby relies heavily on ED1 and ED2 for filling its international aid cohort; RD is hyper-competitive.</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AP9" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. CROSS-REGISTRATION AT MIT: Wellesley students take unlimited computer science, AI, and engineering classes at MIT with full shuttle transport. 100% full-ride funding. High visa confidence when full funding is reflected on I-20.</t>
+          <t>MIT CROSS-REGISTRATION + FULL NEED (r/IntltoUSA Consensus): Premier women's college meeting 100% demonstrated need with zero loans. Students take unlimited Computer Science, AI, and Engineering classes at MIT with dedicated shuttle service. Strong historical track record of admitting Bangladeshi women with full aid in ED.</t>
         </is>
       </c>
       <c r="AQ9" s="7" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. FREE TUITION PLEDGE: Families under $150k income receive free tuition! ABET-accredited engineering at a premier liberal arts institution. Zero loans in aid packages. High visa confidence when full funding is reflected on I-20.</t>
+          <t>FREE TUITION PLEDGE (&lt;$150K) (r/IntltoUSA Consensus): Smith guarantees free tuition for families under $150k and provides ABET-accredited engineering at a women's college. All-grant aid packages (zero loans). Five College Consortium with Amherst, UMass, Mount Holyoke, and Hampshire.</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="AP11" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: The Big Three of US Liberal Arts. Huge endowments, world-class faculty access. Need-aware for int'ls, but once admitted, financial aid packages are unmatched (all grants, zero loans, health insurance, flights).</t>
+          <t>ALL-INCLUSIVE FINANCIAL AID (r/IntltoUSA Consensus): Williams offers what many consider the most generous aid package in higher education: covers tuition, room, board, health insurance, course books, and free campus event access. Because it is need-aware for internationals, Regular Decision acceptance with $0 EFC is below 2%; applying Early Decision maximizes admit probability.</t>
         </is>
       </c>
       <c r="AQ11" s="7" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: Sub-2% int'l admit rate; purely merit/Olympiad driven. If you have international Olympiads or first-author AI papers, you have a puncher's chance. 100% Need-blind with zero loans.</t>
+          <t>NEED-BLIND MERITOCRACY (r/IntltoUSA Consensus): Sub-2% international admit rate; evaluates applicants completely need-blind. MIT requires its own application portal and mandatory SAT/ACT scores. Successful applicants typically present national or international Olympiad medals, first-author research, or world-class technical projects. Full need met with $0 loans.</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AP13" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Technical Project Upload: Upload your research paper abstract or scientific manuscript and live GitHub repository links (web platforms, mobile apps, and technical repositories) directly to your application portal under 'Supplemental Research Materials'. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>STEM &amp; CS POWERHOUSE LAC (r/IntltoUSA Consensus): Carleton has an elite track record of sending graduates to top PhD programs and Silicon Valley tech firms. Meets 100% demonstrated need for admitted internationals; ED application provides a massive statistical advantage over RD.</t>
         </is>
       </c>
       <c r="AQ13" s="7" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Part of the elite 9 need-blind universities. Brown and Notre Dame recently transitioned to international need-blind. Full rides cover 100% on I-20, guaranteeing effortless F-1 visa clearance at Dhaka Embassy.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): University of Notre Dame maintains a verified policy for international students (Need-Blind for all undergraduate applicants worldwide (effec...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="AP15" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: The Big Three of US Liberal Arts. Huge endowments, world-class faculty access. Need-aware for int'ls, but once admitted, financial aid packages are unmatched (all grants, zero loans, health insurance, flights).</t>
+          <t>INTELLECTUAL POWERHOUSE (r/IntltoUSA Consensus): Meets 100% demonstrated need with zero loans. Renowned for its rigorous Honors program and generous summer research grants ($5,500+). Need-aware for internationals; ED1 and ED2 are significantly more favorable than RD for full funding.</t>
         </is>
       </c>
       <c r="AQ15" s="7" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Known for producing leaders in finance, tech, and public policy. Highly selective for int'ls, but their financial aid packages are bulletproof ($0 loans, full living allowance). Applying ED1 or ED2 provides a massive boost over RD.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Claremont McKenna College (CMC) maintains a verified policy for international students (Need-aware for int'ls; meets 100% of demonstrated financial ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="AP17" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>GLOBAL PERSPECTIVE &amp; FULL AID (r/IntltoUSA Consensus): Renowned for international relations, languages, and environmental studies. Meets 100% demonstrated need for admitted students with zero loans. Early Decision is strongly recommended for full aid applicants.</t>
         </is>
       </c>
       <c r="AQ17" s="7" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: The legendary Need-Blind Holy Trinity. True $0 family contribution guaranteed. Princeton PFAA is 100% free. Admissions is holistic but requires world-class spike or national rank.</t>
+          <t>LEGENDARY FULL RIDE (r/IntltoUSA Consensus): 100% need-blind for all international applicants. Families earning under $85,000 pay $0, and receive a $2,000 start-up grant for initial campus expenses. While acceptance is under 3% globally, admitted Bangladeshi students receive complete funding covering tuition, room, board, and health insurance.</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AP19" s="7" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: The legendary Need-Blind Holy Trinity. True $0 family contribution guaranteed. Princeton PFAA is 100% free. Admissions is holistic but requires world-class spike or national rank.</t>
+          <t>TOP NEED-BLIND IVY (r/IntltoUSA Consensus): 100% need-blind for international students. Families under $75,000 pay $0 parent share, and receive an additional start-up allowance. SCEA is restrictive, but RD admits high-need South Asian scholars with pronounced academic or social impact spikes.</t>
         </is>
       </c>
       <c r="AQ19" s="7" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: The Big Three of US Liberal Arts. Huge endowments, world-class faculty access. Need-aware for int'ls, but once admitted, financial aid packages are unmatched (all grants, zero loans, health insurance, flights).</t>
+          <t>CLAREMONT CONSORTIUM LEADER (r/IntltoUSA Consensus): Highest endowment per student among liberal arts colleges; meets 100% of demonstrated need with zero loans. Benefits from the 5-College Claremont Consortium (Harvey Mudd, Claremont McKenna, Scripps, Pitzer). Highly selective, but financial aid packages are flawless.</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AP21" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>INCLUSIVE EXCELLENCE (r/IntltoUSA Consensus): Meets 100% demonstrated need with zero loans. Test-optional for over three decades. Generous with international funding, particularly in Early Decision.</t>
         </is>
       </c>
       <c r="AQ21" s="7" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Part of the elite 9 need-blind universities. Brown and Notre Dame recently transitioned to international need-blind. Full rides cover 100% on I-20, guaranteeing effortless F-1 visa clearance at Dhaka Embassy.</t>
+          <t>NEED-BLIND + FREE ISFAA (r/IntltoUSA Consensus): Transitioned to international need-blind in 2022 thanks to a $90M anonymous endowment. Crucially, Dartmouth allows international students to submit the free ISFAA PDF directly to the portal instead of the expensive CSS Profile. ED provides an exceptional advantage for high-need applicants; generous winter gear and travel support provided.</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="AP23" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>KARSH SCHOLARS HUBS (r/IntltoUSA Consensus): While Duke is need-aware for international need-based aid, the Karsh International Scholars Program provides a comprehensive full ride (tuition, room, board, mandatory fees, and funding for 3 summer research/service experiences). Demonstrating exceptional global leadership and academic impact is essential.</t>
         </is>
       </c>
       <c r="AQ23" s="7" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>BIG TEN PREMIER &amp; LAKEFRONT CAMPUS (r/IntltoUSA Consensus): Meets 100% demonstrated need for international admits with zero loans. Renowned McCormick School of Engineering and Medill School of Journalism. Highly competitive for $0 EFC in RD; ED provides the highest statistical yield.</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="AP25" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly prized because it gives a Columbia University education and Ivy League diploma with the individualized mentorship of a top-tier LAC. Extremely generous full rides for admitted international women.</t>
+          <t>COLUMBIA AFFILIATION &amp; WOMEN'S LEADERSHIP (r/IntltoUSA Consensus): Barnard is an independent women's liberal arts college affiliated with Columbia University. Students have full cross-registration across all Columbia undergraduate courses, libraries, and student clubs, receiving a diploma signed by Columbia University. Meets 100% demonstrated need for admitted internationals; need-aware. ED1 provides the highest statistical chance for full-aid seekers.</t>
         </is>
       </c>
       <c r="AQ25" s="7" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Maker / Research Portfolio: Highly recommended! Submit Slideroom maker portfolio showcasing GitHub repositories, live software/web demo links, competitive programming profiles, and peer-reviewed research manuscripts or abstracts via applicant portal. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COLUMBIA COLLEGE &amp; SEAS (r/IntltoUSA Consensus): Meets 100% demonstrated need with zero loans in NYC. Need-aware for internationals, so RD acceptance rate with $0 EFC is below 2%. Columbia College requires the 100-year-old Core Curriculum (intense Western canon literature &amp; philosophy), whereas Columbia SEAS emphasizes engineering/applied science. ED application is strongly advised for high-aid applicants.</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="AP27" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>PROGRESSIVE CURRICULUM &amp; FULL NEED (r/IntltoUSA Consensus): Meets 100% demonstrated need for admitted students with generous grants. Need-aware for internationals; selective in RD, but strong ED admit rate.</t>
         </is>
       </c>
       <c r="AQ27" s="7" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>FREEMAN ASIAN SCHOLARS (r/IntltoUSA Consensus): In addition to generous need-based aid meeting 100% of demonstrated need, Wesleyan's prestigious Freeman Asian Scholars Program awards full-tuition scholarships to Asian students. Open curriculum and vibrant arts/STEM synergy.</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AP29" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>THE COLGATE COMMITMENT (r/IntltoUSA Consensus): Covers 100% of tuition for families earning under $80,000, and meets 100% demonstrated need with zero loans. Need-aware for international students; ED round provides significant admissions leverage.</t>
         </is>
       </c>
       <c r="AQ29" s="7" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>TWIN CITIES METRO &amp; KOFI ANNAN SCHOLARS (r/IntltoUSA Consensus): Located in Minneapolis-St. Paul; meets 100% of demonstrated need. Offers the Kofi Annan International Scholarship. Heavily favors students with an internationalist worldview and demonstrated community impact.</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="AP31" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>LITERARY RIGOR &amp; HIGH ENDOWMENT AID (r/IntltoUSA Consensus): Home of the Kenyon Review and world-renowned writing culture, alongside strong STEM research. Meets high demonstrated need for international scholars. Community consensus highlights that applying Early Decision (ED1/ED2) offers a 3x admissions boost over RD.</t>
         </is>
       </c>
       <c r="AQ31" s="7" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Part of the elite 9 need-blind universities. Brown and Notre Dame recently transitioned to international need-blind. Full rides cover 100% on I-20, guaranteeing effortless F-1 visa clearance at Dhaka Embassy.</t>
+          <t>NEWLY NEED-BLIND (r/IntltoUSA Consensus): Brown officially transitioned to need-blind admissions for all international students starting with the Class of 2029. Offers the legendary Open Curriculum with no core requirements. Aid packages are completely loan-free and cover full demonstrated financial need.</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="AP33" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Union College maintains a verified policy for international students (Need-Aware for international applicants; meets 100% demonstr...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ33" s="7" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>THE DAVIDSON TRUST (r/IntltoUSA Consensus): First liberal arts college to eliminate loans from financial aid packages. In addition to 100% need-based aid, the John M. Belk Scholarship provides a full ride plus two $6,000 summer stipends. Strong honor code and faculty mentorship.</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AP35" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>OPEN CURRICULUM &amp; ZERO LOANS (r/IntltoUSA Consensus): Meets 100% demonstrated need with zero loans. No core curriculum requirements. Writing-intensive approach prepares graduates exceptionally well for graduate fellowships.</t>
         </is>
       </c>
       <c r="AQ35" s="7" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>TRI-CO CONSORTIUM RIGOR (r/IntltoUSA Consensus): Meets 100% demonstrated need with zero loans. Full cross-registration with Bryn Mawr and Swarthmore, plus engineering partnerships with Caltech and Penn. Governed by a student-run Honor Code with unproctored exams.</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="AP37" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Washington University in St. Louis (WashU) maintains a verified policy for international students (Need-Aware for intls; meets 100% demonstrated need. Also off...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ37" s="7" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Richmond Scholars (Dec 1) is a 100% pure merit full ride. Highly recommended by r/IntltoUSA counselors because it bypasses international need quotas.</t>
+          <t>RICHMOND SCHOLARS FULL RIDE (r/IntltoUSA Consensus): Meets 100% demonstrated need for admitted internationals. Furthermore, the Richmond Scholars Program awards 25 full-ride merit scholarships (tuition, room, board, and priority registration) to applicants who submit by December 1. Highly generous on campus.</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="AP39" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Legendary intellectual rigor. The free UChicago Financial Aid Worksheet is beloved on r/IntltoUSA because it bypasses CSS Profile fees. Generous packages, but applicants MUST declare need on initial Common App.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): University of Chicago (UChicago) maintains a verified policy for international students (Need-aware for int'ls; meets 100% of demonstrated financial ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ39" s="7" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Whitman College maintains a verified policy for international students (Need-aware; meets 100% demonstrated need for a selective poo...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="AP41" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: 'The most mythical college in America.' Zero cost, intense intellectual debates, manual labor on an isolated desert ranch. If you get in, you are practically guaranteed transfer into an Ivy League university with full funding.</t>
+          <t>HYPER-ELITE ALTERNATIVE (r/IntltoUSA Consensus): Deep Springs accepts only 12–15 students annually onto a working cattle ranch. Every admitted student receives a 100% full ride covering tuition, room, and board. Requires extensive philosophical essays and intense dedication to manual labor and self-governance. Highly respected at top Ivy transfer destinations.</t>
         </is>
       </c>
       <c r="AQ41" s="7" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Staple: Known as the 'Holy Trinity of Zero-Cost Application LACs'. $0 application fee, free ISFAA PDF upload, and extremely generous institutional aid pools ($55k-$70k/yr) for high-stat South Asian STEM students.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): DePauw University maintains a verified policy for international students (Need-aware; offers large merit awards and need-based aid for...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="AP43" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Demonstrated Interest: CRITICAL! This institution tracks demonstrated interest heavily. Register for virtual info sessions, student webinars, open all admissions emails, and schedule an online international student interview. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>FREE TUITION PLEDGE (&lt;$150K) (r/IntltoUSA Consensus): Smith guarantees free tuition for families under $150k and provides ABET-accredited engineering at a women's college. All-grant aid packages (zero loans). Five College Consortium with Amherst, UMass, Mount Holyoke, and Hampshire.</t>
         </is>
       </c>
       <c r="AQ43" s="7" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>THE RICE INVESTMENT &amp; HOUSTON TECH (r/IntltoUSA Consensus): Generous endowment in Houston, Texas. Need-aware for internationals, but guarantees 100% demonstrated need with zero loans. Residential college system creates a close-knit community. High SAT scores (1520+) and research supplements strongly recommended.</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="AP45" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COLLEGE HOUSES &amp; FREE ISFAA (r/IntltoUSA Consensus): Franklin &amp; Marshall meets 100% demonstrated need and accepts the free ISFAA PDF uploaded to the portal. Features the distinctive College House residential system and strong pre-med / data science tracks. Need-aware in RD, so ED1/ED2 offers the highest admit yield.</t>
         </is>
       </c>
       <c r="AQ45" s="7" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Bucknell University maintains a verified policy for international students (Need-aware; meets 100% demonstrated need for a selective coh...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="AP47" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>PORTER SCHOLARSHIPS &amp; FULL AID (r/IntltoUSA Consensus): Meets 100% demonstrated need for admitted students. Offers the Porter Presidential Scholarship in Science and Mathematics ($60,000+). Accepts the free ISFAA PDF directly in the applicant portal.</t>
         </is>
       </c>
       <c r="AQ47" s="7" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: 'Bryn Mawr meets 100% need for admitted int'ls and having UPenn engineering cross-registration gives you Ivy-level CS resources at an elite LAC.'</t>
+          <t>HISTORIC WOMEN'S STEM LEADER (r/IntltoUSA Consensus): Meets 100% demonstrated need with high international enrollment (&gt;25%). Enjoys full academic reciprocity with Haverford and Penn. Accepts fee waiver requests and evaluates applications holistically.</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="AP49" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>WOODRUFF SCHOLARS PROGRAM (r/IntltoUSA Consensus): Emory meets 100% demonstrated need for admitted students, and the Emory University Woodruff Scholars Program awards full tuition, fees, and a $14,000 annual living stipend to international nominees. Priority deadline is November 15.</t>
         </is>
       </c>
       <c r="AQ49" s="7" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Technical Project Upload: Upload your research paper abstract or scientific manuscript and live GitHub repository links (web platforms, mobile apps, and technical repositories) directly to your application portal under 'Supplemental Research Materials'. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>MARQUIS FELLOWSHIP &amp; ABET ENGINEERING (r/IntltoUSA Consensus): Lafayette combines top-tier ABET-accredited engineering with a liberal arts college. Meets 100% demonstrated need with zero loans. Offers the Marquis Fellowship (full tuition) and Marquis Scholars awards. Applying ED is critical for full-aid candidates.</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="AP51" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Maker / Research Portfolio: Highly recommended! Submit Slideroom maker portfolio showcasing GitHub repositories, live software/web demo links, competitive programming profiles, and peer-reviewed research manuscripts or abstracts via applicant portal. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>SILICON VALLEY SUPER-REACH (r/IntltoUSA Consensus): Evaluates international aid applicants need-aware, but meets 100% demonstrated need with zero loans. Single-Choice Early Action (SCEA) does not provide a statistically significant aid advantage over RD. Admitted South Asian students typically have exceptional entrepreneurial, CS/AI research, or global policy spikes. Health insurance and campus room &amp; board fully covered on Form I-20.</t>
         </is>
       </c>
       <c r="AQ51" s="7" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. DUAL CAMPUS ACCESS (DUKE &amp; UNC): Robertson Scholars take classes and live on both Duke and UNC campuses with all expenses, tuition, housing, and 3 summer experiences 100% paid! High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): University of North Carolina at Chapel Hill (UNC - Robertson Scholars) maintains a verified policy for international students (The Robertson Scholars Program provides a comprehensive 100%...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AP53" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. 40%+ INTERNATIONAL COHORT! The Soka Opportunity Plan covers 100% of tuition for families earning under $200,000. Uses its own free financial aid form. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Soka University of America (SUA) maintains a verified policy for international students (Soka Opportunity Plan: 100% Full Tuition covered for all adm...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ53" s="7" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. 25%+ INTERNATIONAL STUDENT BODY! Extremely welcoming to South Asian students. Access to UMass Amherst CS courses via Five-College Consortium. High visa confidence when full funding is reflected on I-20.</t>
+          <t>INTERNATIONAL INCLUSIVITY LEADER (r/IntltoUSA Consensus): High proportion of international students (&gt;25%). Very generous with need-based grants and merit scholarships. Five College Consortium member; strong community support for South Asian applicants.</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="AP55" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. DO NOT SUBMIT CSS PROFILE: Pitzer uses its own 100% FREE Pitzer International Financial Aid Application (PIFAA)! Cross-registration at Harvey Mudd College for CS &amp; Engineering. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Pitzer College maintains a verified policy for international students (Need-aware for int'ls; meets 100% of demonstrated financial ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ55" s="7" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>SAMSON FELLOWSHIP &amp; FULL NEED (r/IntltoUSA Consensus): Meets 100% demonstrated need. Offers the Samson Environmental &amp; International Fellowships (full rides). Strong engineering ABET accredited program at a liberal arts institution. ED is strongly advised.</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="AP57" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Lehigh University maintains a verified policy for international students (Need-aware; meets 100% demonstrated need for a selected pool...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ57" s="7" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Connecticut College maintains a verified policy for international students (Need-Aware for international applicants; meets 100% demonstr...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="AP59" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): College of the Atlantic (COA) maintains a verified policy for international students (Need-aware; meets 100% demonstrated need for admitted intern...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ59" s="7" t="inlineStr">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Staple: Known as the 'Holy Trinity of Zero-Cost Application LACs'. $0 application fee, free ISFAA PDF upload, and extremely generous institutional aid pools ($55k-$70k/yr) for high-stat South Asian STEM students.</t>
+          <t>DENISON MERIT + NEED / YIELD SENSITIVITY (r/IntltoUSA Consensus): Extremely popular among Bangladeshi applicants. Offers zero application fees, accepts the free ISFAA PDF, and stacks merit awards up to $45,000–$55,000/yr. In Regular Decision, high-stat applicants (1500+ SAT) requesting full aid face heavy yield protection unless they demonstrate active interest through virtual interviews or campus webinars.</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="AP61" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: One of the most intellectual LACs in New York. Zero application fee and free ISFAA makes it a favorite on r/IntltoUSA. High aid awards ($50k-$70k/yr) given to students with genuine research spikes.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Bard College maintains a verified policy for international students (Meets high demonstrated need; awards International Peace Sch...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ61" s="7" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>FREEMAN ASIAN SCHOLARS (r/IntltoUSA Consensus): In addition to generous need-based aid meeting 100% of demonstrated need, Wesleyan's prestigious Freeman Asian Scholars Program awards full-tuition scholarships to Asian students. Open curriculum and vibrant arts/STEM synergy.</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="AP63" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>PREMIER MERIT COMPETITION (r/IntltoUSA Consensus): Vanderbilt meets 100% of demonstrated need with zero loans (Opportunity Vanderbilt). Additionally, the Cornelius Vanderbilt, Chancellor's, and Ingram Scholarships provide full-tuition merit awards plus summer research stipends. Must apply by the December 1 priority merit deadline.</t>
         </is>
       </c>
       <c r="AQ63" s="7" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>PRE-MED &amp; CS/BIOMEDICAL GIANT (r/IntltoUSA Consensus): Boosted by Michael Bloomberg's historic $1.8B gift, JHU meets 100% demonstrated need with all-grant packages (no loans). Need-aware for internationals, but ED1 and ED2 offer meaningful acceptance advantages. Admitted students receive comprehensive medical insurance and research grants.</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="AP65" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Maker / Research Portfolio: Highly recommended! Submit Slideroom maker portfolio showcasing GitHub repositories, live software/web demo links, competitive programming profiles, and peer-reviewed research manuscripts or abstracts via applicant portal. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>INTERDISCIPLINARY EXCELLENCE (r/IntltoUSA Consensus): Meets 100% demonstrated need with all-grant aid packages (zero loans). Home to Wharton, Engineering, and Vagelos programs. Highly selective for international aid applicants in RD; ED provides a clear statistical boost. Interviews conducted via Penn Alumni Interview Program.</t>
         </is>
       </c>
       <c r="AQ65" s="7" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="AP66" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Maker / Research Portfolio: Highly recommended! Submit Slideroom maker portfolio showcasing GitHub repositories, live software/web demo links, competitive programming profiles, and peer-reviewed research manuscripts or abstracts via applicant portal. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>DIVERSE COLLEGES &amp; ZERO LOANS (r/IntltoUSA Consensus): Meets 100% demonstrated need for admitted internationals. Students apply directly to specific undergraduate colleges (College of Engineering, Arts &amp; Sciences, Dyson Business). Need-aware for internationals; accepts CSS Profile or free institutional fee waiver requests. Strong South Asian student association.</t>
         </is>
       </c>
       <c r="AQ66" s="3" t="inlineStr">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="AP67" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. HARVEY MUDD CS ACCESS: Scripps students take full Computer Science and Engineering courses at neighboring Harvey Mudd College! Meets 100% demonstrated need. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Scripps College maintains a verified policy for international students (Need-aware for int'ls; meets 100% of demonstrated financial ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ67" s="7" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="AP68" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Demonstrated Interest: CRITICAL! This institution tracks demonstrated interest heavily. Register for virtual info sessions, student webinars, open all admissions emails, and schedule an online international student interview. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Dickinson College maintains a verified policy for international students (Need-aware; very generous financial aid and merit awards for...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ68" s="3" t="inlineStr">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="AP69" s="7" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Staple: Known as the 'Holy Trinity of Zero-Cost Application LACs'. $0 application fee, free ISFAA PDF upload, and extremely generous institutional aid pools ($55k-$70k/yr) for high-stat South Asian STEM students.</t>
+          <t>THE #1 INDEPENDENT STUDY COLLEGE (r/IntltoUSA Consensus): Every senior completes a mentored, year-long Independent Study research thesis. Accepts free ISFAA, waives application fees, and offers substantial international scholarships. High yield-protection in RD; early engagement is critical.</t>
         </is>
       </c>
       <c r="AQ69" s="7" t="inlineStr">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Demonstrated Interest: CRITICAL! This institution tracks demonstrated interest heavily. Register for virtual info sessions, student webinars, open all admissions emails, and schedule an online international student interview. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Gettysburg College maintains a verified policy for international students (Need-aware; generous with international aid packages, combin...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="AP71" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Hidden gem for female applicants. Cross-registration at Emory allows taking Emory CS and data science classes. The Woodruff Scholarship is a full ride covering all expenses.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Agnes Scott College maintains a verified policy for international students (Woodruff Scholars Program covers 100% Full Ride (tuition, ro...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ71" s="7" t="inlineStr">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="AP72" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly distinctive Oxford tutorial model. Perfect for independent researchers, programmers, and writers. Generous international aid pool, very welcoming to South Asian students.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Sarah Lawrence College maintains a verified policy for international students (Meets high demonstrated need; generous international package...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ72" s="3" t="inlineStr">
@@ -18225,7 +18225,7 @@
       </c>
       <c r="AP73" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Demonstrated Interest: CRITICAL! This institution tracks demonstrated interest heavily. Register for virtual info sessions, student webinars, open all admissions emails, and schedule an online international student interview. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>ACCESSIBLE HIGH AID TARGET (r/IntltoUSA Consensus): Free application, prompt admission decisions, and stacked international scholarships. Meets high need; exceptional choice for students with partial/moderate family contributions ($5k-$15k) seeking guaranteed generous funding.</t>
         </is>
       </c>
       <c r="AQ73" s="7" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="AP74" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Maker / Research Portfolio: Highly recommended! Submit Slideroom maker portfolio showcasing GitHub repositories, live software/web demo links, competitive programming profiles, and peer-reviewed research manuscripts or abstracts via applicant portal. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Tufts University maintains a verified policy for international students (Need-Aware for international applicants; meets 100% demonstr...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ74" s="3" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="AP75" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Reed College maintains a verified policy for international students (Need-aware; meets 100% demonstrated need for admitted intern...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ75" s="7" t="inlineStr">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="AP76" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. ACCEPTS FREE ISFAA PDF FORM! The Block Plan allows intensive deep-dive coding sprints. Meets 100% demonstrated need with zero loans. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Colorado College maintains a verified policy for international students (Need-aware for int'ls; meets 100% of demonstrated financial ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ76" s="3" t="inlineStr">
@@ -19193,7 +19193,7 @@
       </c>
       <c r="AP77" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>PROGRESSIVE HERITAGE &amp; MULTI-MILLION AID POOL (r/IntltoUSA Consensus): Oberlin earmarks a dedicated multi-million dollar annual international grant pool. Unique integration between the College of Arts &amp; Sciences and the world-class Oberlin Conservatory. ED is highly recommended for full-aid applicants.</t>
         </is>
       </c>
       <c r="AQ77" s="7" t="inlineStr">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="AP78" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): St. Lawrence University maintains a verified policy for international students (Need-aware; very generous international aid packages combini...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ78" s="3" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="AP79" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Demonstrated Interest: CRITICAL! This institution tracks demonstrated interest heavily. Register for virtual info sessions, student webinars, open all admissions emails, and schedule an online international student interview. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>THE K-PLAN &amp; EXPEDITIONARY LEARNING (r/IntltoUSA Consensus): The renowned K-Plan integrates rigorous academics, mandatory study abroad, and hands-on career externships. Free Common App application and generous international financial aid up to $40,000+/yr.</t>
         </is>
       </c>
       <c r="AQ79" s="7" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="AP80" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>PROGRAM OF EMPHASIS (POE) (r/IntltoUSA Consensus): Allows students to customize their own POE (degree) with dual academic advisors. Zero application fee, friendly international admissions office, and stacked merit/need packages up to $42,000/yr. Excellent stepping stone to top STEM PhD programs.</t>
         </is>
       </c>
       <c r="AQ80" s="3" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="AP81" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Hendrix College maintains a verified policy for international students (Need-aware; offers large international merit awards and need...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ81" s="7" t="inlineStr">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="AP82" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Demonstrated Interest: CRITICAL! This institution tracks demonstrated interest heavily. Register for virtual info sessions, student webinars, open all admissions emails, and schedule an online international student interview. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMBINATORIAL DOUBLE MAJORS (r/IntltoUSA Consensus): Famous for requiring a major and minor in different divisions (e.g. Computer Science + Economics). Zero application fee on Common App, generous merit scholarships ($35,000+) plus need-based aid. Very accessible target for South Asian students.</t>
         </is>
       </c>
       <c r="AQ82" s="3" t="inlineStr">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="AP83" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>GLOBAL CITIZENSHIP &amp; EPIC ADVANTAGE (r/IntltoUSA Consensus): Strong tradition of internationalist education. Generous need-based aid for international students, with the Epic Advantage providing $5,000 guaranteed funding for internships or research. Free application on Common App.</t>
         </is>
       </c>
       <c r="AQ83" s="7" t="inlineStr">
@@ -20887,7 +20887,7 @@
       </c>
       <c r="AP84" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>NOBEL CONFERENCE &amp; ACCESSIBLE AID (r/IntltoUSA Consensus): Hosts the prestigious annual Nobel Conference. Very welcoming to international applicants with zero application fees and stacked Global Leader scholarships ($30,000–$40,000/yr). Excellent target for students seeking high scholarship probability.</t>
         </is>
       </c>
       <c r="AQ84" s="3" t="inlineStr">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="AP85" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Southwestern University maintains a verified policy for international students (Brown Scholars &amp; general aid provide up to Full Tuition and ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ85" s="7" t="inlineStr">
@@ -21371,7 +21371,7 @@
       </c>
       <c r="AP86" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Bennington College maintains a verified policy for international students (Need-aware; very generous international need and merit finan...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ86" s="3" t="inlineStr">
@@ -21613,7 +21613,7 @@
       </c>
       <c r="AP87" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>AUGIE CHOICE &amp; PROMPT ADMISSION (r/IntltoUSA Consensus): Offers $2,000 'Augie Choice' funding for research or internships. Very generous international scholarships (up to $35,000+/yr), zero application fee, and free English language waiver policy. High admission reliability.</t>
         </is>
       </c>
       <c r="AQ87" s="7" t="inlineStr">
@@ -21855,7 +21855,7 @@
       </c>
       <c r="AP88" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Merit Scholarship Deadline: Must submit application by the strict Merit Deadline (typically Dec 1 or Nov 15) to be considered for premier full-ride/full-tuition merit scholarships (e.g. Richmond Scholars, BU Trustee, Stamps, Hunt). | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>TRUSTEE SCHOLARSHIP (r/IntltoUSA Consensus): USC's Trustee Scholarship provides full tuition (~100 recipients annually) and is open to international applicants. Strict early deadline of December 1. High SAT (1500+) and exceptional leadership essays are critical for interview selection.</t>
         </is>
       </c>
       <c r="AQ88" s="3" t="inlineStr">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="AP89" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Sewanee: The University of the South maintains a verified policy for international students (Need-aware; offers generous need and merit aid to internatio...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ89" s="7" t="inlineStr">
@@ -22339,7 +22339,7 @@
       </c>
       <c r="AP90" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Demonstrated Interest: CRITICAL! This institution tracks demonstrated interest heavily. Register for virtual info sessions, student webinars, open all admissions emails, and schedule an online international student interview. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>CONVERSATION ACADEMICS &amp; HIGH STEM PLACEMENT (r/IntltoUSA Consensus): Renowned for mathematics, natural sciences, and the renowned St. Olaf Choir. Offers generous international merit scholarships ($25,000–$42,000) and meets demonstrated financial need for admitted students. Zero application fee and prompt decision turnaround. Test-optional friendly.</t>
         </is>
       </c>
       <c r="AQ90" s="3" t="inlineStr">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AP91" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Furman University maintains a verified policy for international students (Offers full ride merit scholarships (Townes/Hollingsworth) a...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ91" s="7" t="inlineStr">
@@ -22823,7 +22823,7 @@
       </c>
       <c r="AP92" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Demonstrated Interest: CRITICAL! This institution tracks demonstrated interest heavily. Register for virtual info sessions, student webinars, open all admissions emails, and schedule an online international student interview. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Rhodes College maintains a verified policy for international students (Need-aware; offers competitive merit scholarships and need-b...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ92" s="3" t="inlineStr">
@@ -23065,7 +23065,7 @@
       </c>
       <c r="AP93" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Centre College maintains a verified policy for international students (Lincoln Scholars Program provides competitive Full Ride to i...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ93" s="7" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="AP94" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Wabash College maintains a verified policy for international students (Need-aware; exceptionally generous to international men with...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ94" s="3" t="inlineStr">
@@ -23549,7 +23549,7 @@
       </c>
       <c r="AP95" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly respected on r/IntltoUSA. The Wien International Scholarship Program is one of the oldest and most prestigious full rides in the US. If you apply for aid, admissions is selective, but once admitted, they fund you fully without loans.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Brandeis University maintains a verified policy for international students (Need-aware for int'ls; meets 100% of demonstrated need for a...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ95" s="7" t="inlineStr">
@@ -23791,7 +23791,7 @@
       </c>
       <c r="AP96" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly regarded in the Pacific Northwest tech and environmental community. Accepts free ISFAA PDF on applicant portal, saving CSS Profile costs. Generous financial aid for strong applicants.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Lewis &amp; Clark College maintains a verified policy for international students (Meets high demonstrated need; international financial aid aw...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ96" s="3" t="inlineStr">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="AP97" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: 100% Test-Free policy is real. Does not look at SAT scores. Focuses exclusively on Olympiads, AMC/AIME math scores, published research, and 5.0 GPA. Full ride covers all costs.</t>
+          <t>TEST-FREE STEM SUPER-ELITE (r/IntltoUSA Consensus): Caltech has enacted a complete test-free moratorium—SAT/ACT scores will NOT be reviewed. Freshman class size is tiny (~230 students total). Financial aid for internationals is need-aware and met 100% with zero loans, but fewer than 5–10 high-need international students are admitted annually. International Olympiad medals (IPhO, IMO, IOI) or published original research are essentially mandatory.</t>
         </is>
       </c>
       <c r="AQ97" s="7" t="inlineStr">
@@ -24275,7 +24275,7 @@
       </c>
       <c r="AP98" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: The only college in America guaranteeing 100% Tuition Promise to EVERY single admitted student. Admits ~30 int'ls/yr on pure $0 EFC. Requires rigorous financial documentation and on-campus work.</t>
+          <t>LEGENDARY WORK COLLEGE (r/IntltoUSA Consensus): Berea provides 100% Tuition Promise Scholarships ($50,000+) to every single admitted student, with room, board, and books covered through the mandatory student work program (10-15 hrs/week). ADMISSIONS REALITY: Berea strictly admits only 1–2 students per country per year (sometimes 1 every 2 years from Bangladesh). They specifically screen against wealthy families; if your family income exceeds ~$5,000–$8,000/yr, your odds drop dramatically.</t>
         </is>
       </c>
       <c r="AQ98" s="3" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="AP99" s="7" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: 'A staple safety/target for high-need international students.' Free application, accepts free ISFAA, and awards huge scholarship packages ($40k-$55k/year) very reliably.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Lawrence University maintains a verified policy for international students (Meets high demonstrated need; international awards range fro...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ99" s="7" t="inlineStr">
@@ -24759,7 +24759,7 @@
       </c>
       <c r="AP100" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: 'The Silicon Valley cheat code.' SCU engineers get hired by Google, Apple, and Meta at staggering rates. The Johnson Scholarship provides a 100% full ride + $10k startup stipend for software builders.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Santa Clara University (SCU) maintains a verified policy for international students (Johnson Scholars Program covers 100% Full Ride (tuition, roo...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ100" s="3" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="AP101" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Merit Scholarship Deadline: Must submit application by the strict Merit Deadline (typically Dec 1 or Nov 15) to be considered for premier full-ride/full-tuition merit scholarships (e.g. Richmond Scholars, BU Trustee, Stamps, Hunt). | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>STAMPS SCHOLARSHIP (r/IntltoUSA Consensus): University of Miami awards the premier Stamps Scholarship to top international applicants, covering full tuition, room, board, health insurance, textbooks, and a $12,000 enrichment fund. Early Action submission is mandatory.</t>
         </is>
       </c>
       <c r="AQ101" s="7" t="inlineStr">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="AP102" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Merit Scholarship Deadline: Must submit application by the strict Merit Deadline (typically Dec 1 or Nov 15) to be considered for premier full-ride/full-tuition merit scholarships (e.g. Richmond Scholars, BU Trustee, Stamps, Hunt). | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): University of Virginia (UVA) maintains a verified policy for international students (Jefferson Scholars open to international students nominated ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ102" s="3" t="inlineStr">
@@ -25485,7 +25485,7 @@
       </c>
       <c r="AP103" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Michigan State University (MSU) maintains a verified policy for international students (Offers competitive Presidential, You Are Welcome Here, and R...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ103" s="7" t="inlineStr">
@@ -25727,7 +25727,7 @@
       </c>
       <c r="AP104" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Muhlenberg College maintains a verified policy for international students (Need-aware; meets demonstrated need for selected internation...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ104" s="3" t="inlineStr">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="AP105" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Top Boston powerhouse. The Gabelli Presidential Scholarship is open to international applicants without restriction. Highly competitive, but provides an Ivy-equivalent undergraduate cohort experience.</t>
+          <t>GABELLI PRESIDENTIAL SCHOLARS (r/IntltoUSA Consensus): Boston College offers 15 full-tuition scholarships plus fully funded summer international experiences. Must apply Early Decision or priority deadline by November 1. Extremely competitive.</t>
         </is>
       </c>
       <c r="AQ105" s="7" t="inlineStr">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="AP106" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Merit Scholarship Deadline: Must submit application by the strict Merit Deadline (typically Dec 1 or Nov 15) to be considered for premier full-ride/full-tuition merit scholarships (e.g. Richmond Scholars, BU Trustee, Stamps, Hunt). | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>REYNOLDS &amp; CARSWELL SCHOLARS (r/IntltoUSA Consensus): Wake Forest offers full-ride merit scholarships (Reynolds, Guy T. Carswell) covering tuition, room, board, and personal stipends. Test-optional pioneer, but interviews are strongly recommended.</t>
         </is>
       </c>
       <c r="AQ106" s="3" t="inlineStr">
@@ -26453,7 +26453,7 @@
       </c>
       <c r="AP107" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee, free ISFAA, and outstanding engineering co-op placement where students earn enough cash to cover living expenses. Full-tuition scholarships available.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Marquette University maintains a verified policy for international students (Père Marquette and Burke Scholarships award up to 100% Full ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ107" s="7" t="inlineStr">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="AP108" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/ApplyingToCollege Consensus: Villanova Presidential Scholarship is one of the premier Catholic full rides in the US. Open to international students without religious restrictions. Requires strong leadership and GPA.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Villanova University maintains a verified policy for international students (Presidential Scholarship covers 100% Full Ride (tuition, roo...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ108" s="3" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="AP109" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Technical Project Upload: Upload your research paper abstract or scientific manuscript and live GitHub repository links (web platforms, mobile apps, and technical repositories) directly to your application portal under 'Supplemental Research Materials'. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Worcester Polytechnic Institute (WPI) maintains a verified policy for international students (Need-aware; offers large merit awards (up to $40,000 - full ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ109" s="7" t="inlineStr">
@@ -27179,7 +27179,7 @@
       </c>
       <c r="AP110" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Technical Project Upload: Upload your research paper abstract or scientific manuscript and live GitHub repository links (web platforms, mobile apps, and technical repositories) directly to your application portal under 'Supplemental Research Materials'. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Case Western Reserve University (CWRU) maintains a verified policy for international students (Need-aware; meets demonstrated need for selected internation...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ110" s="3" t="inlineStr">
@@ -27421,7 +27421,7 @@
       </c>
       <c r="AP111" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Fordham University maintains a verified policy for international students (Cunniffe Presidential Scholarship open to all international ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ111" s="7" t="inlineStr">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="AP112" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: 'The most stubborn testing policy in America—they require every SAT score you've ever taken.' Very small aid budget for int'ls (~35 admitted on aid/yr), but full rides are 100% loan-free if awarded.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Georgetown University maintains a verified policy for international students (Need-aware for int'ls; meets 100% of demonstrated financial ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ112" s="3" t="inlineStr">
@@ -27905,7 +27905,7 @@
       </c>
       <c r="AP113" s="7" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: 'DO NOT apply to CMU Pittsburgh if you have a $0 EFC—they will reject you immediately or give you $0 aid.' Instead, apply to CMU Qatar, which has identical CS curriculum, CMU faculty, identical diploma, and full rides funded by Qatar Foundation.</t>
+          <t>CRITICAL ZERO-AID REALITY (r/IntltoUSA Consensus): Carnegie Mellon explicitly does NOT offer institutional financial aid to undergraduate international students (verified via CDS Section H6: 0 international students receive aid). Every admitted international applicant must provide proof of ability to pay 100% of attendance costs (~$88,000+/year). Do NOT apply here if you require financial aid or a full ride.</t>
         </is>
       </c>
       <c r="AQ113" s="7" t="inlineStr">
@@ -28147,7 +28147,7 @@
       </c>
       <c r="AP114" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Merit Scholarship Deadline: Must submit application by the strict Merit Deadline (typically Dec 1 or Nov 15) to be considered for premier full-ride/full-tuition merit scholarships (e.g. Richmond Scholars, BU Trustee, Stamps, Hunt). | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>TRUSTEE SCHOLARS PROGRAM (r/IntltoUSA Consensus): Boston University offers the Trustee Scholarship (full tuition and fees) to ~20 outstanding international and domestic students. Requires a separate Trustee essay on the Common App and submission by December 1. Need-based aid is extremely limited for internationals.</t>
         </is>
       </c>
       <c r="AQ114" s="3" t="inlineStr">
@@ -28389,7 +28389,7 @@
       </c>
       <c r="AP115" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: 'WARNING: Tulane yield-protects heavily!' If you apply Regular Decision without showing high interest, you get waitlisted. Apply EA or ED, and submit the optional Dec 5 scholarship portfolio to win full tuition.</t>
+          <t>DEANS' HONOR &amp; PAUL TULANE AWARDS (r/IntltoUSA Consensus): Tulane awards full-tuition merit scholarships to top applicants via separate creative portfolio applications (deadline Dec 5). Tulane heavily tracks demonstrated interest—virtual tour attendance and local counselor engagement are strictly monitored.</t>
         </is>
       </c>
       <c r="AQ115" s="7" t="inlineStr">
@@ -28631,7 +28631,7 @@
       </c>
       <c r="AP116" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>DREXEL GLOBAL SCHOLARS (r/IntltoUSA Consensus): Drexel's premier Co-op university model offers the Drexel Global Scholar program, providing full tuition to exceptional international applicants who demonstrate community leadership. Requires an early application and supplemental leadership essay.</t>
         </is>
       </c>
       <c r="AQ116" s="3" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="AP117" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Rollins College maintains a verified policy for international students (Alfond Scholars Program covers 100% Full Ride (Tuition, room...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ117" s="7" t="inlineStr">
@@ -29115,7 +29115,7 @@
       </c>
       <c r="AP118" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. SEMMES FULL-TUITION SCHOLARSHIP: Awarded to top STEM &amp; Computer Science applicants including full tuition and $5,000 research stipend! Uses free Trinity financial form. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Trinity University (San Antonio, TX) maintains a verified policy for international students (Semmes Full-Tuition Scholarship + Tower Scholars (Full Tuiti...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ118" s="3" t="inlineStr">
@@ -29357,7 +29357,7 @@
       </c>
       <c r="AP119" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly rated for CS and quantitative computing. Top starting salaries ($85k+) rivaling Ivy League graduates. The Pinnacle and Global scholarships provide full tuition for top international math and CS applicants.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Stevens Institute of Technology maintains a verified policy for international students (Global Scholars Program and Pinnacle Scholars award up to 10...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ119" s="7" t="inlineStr">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="AP120" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Gorgeous campus above Silicon Beach. Prime recruiting pipelines into tech, entertainment computing, and media AI. Arrupe scholarships provide full tuition.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Loyola Marymount University (LMU) maintains a verified policy for international students (Arrupe Scholarships and Presidential Scholarships award up t...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ120" s="3" t="inlineStr">
@@ -29841,7 +29841,7 @@
       </c>
       <c r="AP121" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Technical Project Upload: Upload your research paper abstract or scientific manuscript and live GitHub repository links (web platforms, mobile apps, and technical repositories) directly to your application portal under 'Supplemental Research Materials'. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Illinois Institute of Technology (Illinois Tech) maintains a verified policy for international students (Offers Full Tuition scholarships (Camras Scholars / Leadersh...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ121" s="7" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="AP122" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly supportive, welcoming campus with zero application fee and free ISFAA. Full-tuition diversity scholarship is realistic for top South Asian students.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Whitworth University maintains a verified policy for international students (International Full-Tuition Diversity Scholarship covers 100%...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ122" s="3" t="inlineStr">
@@ -30325,7 +30325,7 @@
       </c>
       <c r="AP123" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Merit Scholarship Deadline: Must submit application by the strict Merit Deadline (typically Dec 1 or Nov 15) to be considered for premier full-ride/full-tuition merit scholarships (e.g. Richmond Scholars, BU Trustee, Stamps, Hunt). | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Southern Methodist University (SMU) maintains a verified policy for international students (President's Scholars &amp; Hunt Leadership open to international...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ123" s="7" t="inlineStr">
@@ -30567,7 +30567,7 @@
       </c>
       <c r="AP124" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee and free ISFAA. National Alumni scholarship covers full tuition based on academic distinction and an online interview.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Drake University maintains a verified policy for international students (National Alumni Scholarship covers 100% Full Tuition for top...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ124" s="3" t="inlineStr">
@@ -30809,7 +30809,7 @@
       </c>
       <c r="AP125" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: A reliable, generous college in Iowa. The Global Leadership Scholarship is open to all international applicants and awards full tuition based on GPA, SAT, and a Zoom interview.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Coe College maintains a verified policy for international students (Global Leadership Scholarship covers 100% Full Tuition for t...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ125" s="7" t="inlineStr">
@@ -31051,7 +31051,7 @@
       </c>
       <c r="AP126" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee and free ISFAA. Historic reputation, small class sizes, and competitive full-tuition Premier scholarships for high-stat applicants.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Transylvania University maintains a verified policy for international students (William R. Kenan Scholarship and Premier Scholarships cover ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ126" s="3" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="AP127" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Extremely supportive community for debt-averse international students. Milepost One covers full tuition, and the on-campus work program pays toward your living expenses.</t>
+          <t>TUITION-FREE WORK COLLEGE MODEL (r/IntltoUSA Consensus): Covers 100% of tuition through institutional work-study programs. Students work 15 hours weekly on campus to offset tuition costs. Extremely supportive community for resilient, self-directed students seeking zero educational debt.</t>
         </is>
       </c>
       <c r="AQ127" s="7" t="inlineStr">
@@ -31535,7 +31535,7 @@
       </c>
       <c r="AP128" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee and free ISFAA. Prime location in Buckhead Atlanta. The full-tuition scholarship weekend is a realistic target for high-stat international applicants.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Oglethorpe University maintains a verified policy for international students (James Edward Oglethorpe Scholarship covers 100% Full Tuition...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ128" s="3" t="inlineStr">
@@ -31777,7 +31777,7 @@
       </c>
       <c r="AP129" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee, free ISFAA, and generous merit aid. Located 15 minutes from downtown Dallas and the Richardson telecom corridor.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): University of Dallas maintains a verified policy for international students (Trustee Scholarship and Presidential Awards cover up to 100%...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ129" s="7" t="inlineStr">
@@ -32019,7 +32019,7 @@
       </c>
       <c r="AP130" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Temple University maintains a verified policy for international students (President's Scholars awards Full Tuition to top 1% applicant...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ130" s="3" t="inlineStr">
@@ -32261,7 +32261,7 @@
       </c>
       <c r="AP131" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: The Karsh STEM program at Howard is one of the best-funded undergraduate STEM pipelines in the nation. Open to international students, fully covers all tuition and living expenses, and provides dedicated tech mentorship.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Howard University maintains a verified policy for international students (Karsh STEM Scholars Program provides 100% Full Ride (tuition...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ131" s="7" t="inlineStr">
@@ -32503,7 +32503,7 @@
       </c>
       <c r="AP132" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Clark University maintains a verified policy for international students (Presidential LEEP Scholarship awards 100% Full Tuition + roo...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ132" s="3" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="AP133" s="7" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Consensus: 'The ultimate Claremont trap.' Harvey Mudd has world #1 CS starting salaries, but they do NOT meet full need for int'ls. Lifehack: Apply to Pitzer or Scripps (which meet 100% need with no loans) and take all your CS classes at Harvey Mudd for free!</t>
+          <t>AID LIMITATION REALITY (r/IntltoUSA Consensus): While Harvey Mudd meets 100% need for domestic applicants, its international financial aid budget is extremely restricted (often only 1–2 international partial/full awards per incoming class). Admissions for high-need international students is virtually impossible in Regular Decision without exceptional international Olympiad medals.</t>
         </is>
       </c>
       <c r="AQ133" s="7" t="inlineStr">
@@ -32987,7 +32987,7 @@
       </c>
       <c r="AP134" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Cooper Union for the Advancement of Science and Art maintains a verified policy for international students (Every admitted student automatically receives a 50% tuition ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ134" s="3" t="inlineStr">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="AP135" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Maker / Research Portfolio: Highly recommended! Submit Slideroom maker portfolio showcasing GitHub repositories, live software/web demo links, competitive programming profiles, and peer-reviewed research manuscripts or abstracts via applicant portal. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): University of Rochester maintains a verified policy for international students (Meets demonstrated need for admitted internationals. Handler...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ135" s="7" t="inlineStr">
@@ -33471,7 +33471,7 @@
       </c>
       <c r="AP136" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA Lifehack: 'The backdoor into UMass Amherst CS.' Hampshire students have full cross-registration at UMass Amherst (top 15 CS in the world) and Amherst College, free bus transit, zero application fee, and free ISFAA.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Hampshire College maintains a verified policy for international students (Meets high demonstrated need; awards international grants av...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ136" s="3" t="inlineStr">
@@ -33713,7 +33713,7 @@
       </c>
       <c r="AP137" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly respected New England institution. The Roddy Scholarship is one of the top STEM full-tuition awards in Rhode Island, awarded based on math and science excellence.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Providence College maintains a verified policy for international students (Roddy Foundation Scholarship covers 100% Full Tuition for to...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ137" s="7" t="inlineStr">
@@ -33955,7 +33955,7 @@
       </c>
       <c r="AP138" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Top Jesuit university with exceptional business, CS, and engineering placement in New York City and Stamford. The Magis Scholarship provides full tuition for high-stat applicants.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Fairfield University maintains a verified policy for international students (Magis Scholarship covers up to 100% Full Tuition for top 2% ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ138" s="3" t="inlineStr">
@@ -34197,7 +34197,7 @@
       </c>
       <c r="AP139" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Renowned for intense STEM rigor and quantum computing. Generous merit aid up to $45k-$50k/year, but rarely covers 100% full ride for international students without co-op earnings.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Rensselaer Polytechnic Institute (RPI) maintains a verified policy for international students (RPI Leadership Awards and International Merit Scholarships p...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ139" s="7" t="inlineStr">
@@ -34439,7 +34439,7 @@
       </c>
       <c r="AP140" s="3" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Florida Institute of Technology (Florida Tech) maintains a verified policy for international students (Offers substantial Panther Merit Scholarships (up to full tu...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ140" s="3" t="inlineStr">
@@ -34681,7 +34681,7 @@
       </c>
       <c r="AP141" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee and free ISFAA. Close proximity to Seattle's tech giants (Microsoft, Amazon). Dual degree engineering with Columbia and WashU is a huge asset.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): University of Puget Sound maintains a verified policy for international students (Generous international financial aid and merit scholarships ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ141" s="7" t="inlineStr">
@@ -34923,7 +34923,7 @@
       </c>
       <c r="AP142" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Known as one of the most practical and career-focused LACs in America. Very high acceptance rates for international students with strong grades, and packages frequently cover 85%-90% of total costs.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Beloit College maintains a verified policy for international students (Generous international financial aid and merit scholarships ...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ142" s="3" t="inlineStr">
@@ -35165,7 +35165,7 @@
       </c>
       <c r="AP143" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly recommended for students who thrive in intense, focused project sprints rather than juggling 5 classes at once. Free application, generous international aid, very high acceptance rate.</t>
+          <t>DIVERSE COLLEGES &amp; ZERO LOANS (r/IntltoUSA Consensus): Meets 100% demonstrated need for admitted internationals. Students apply directly to specific undergraduate colleges (College of Engineering, Arts &amp; Sciences, Dyson Business). Need-aware for internationals; accepts CSS Profile or free institutional fee waiver requests. Strong South Asian student association.</t>
         </is>
       </c>
       <c r="AQ143" s="7" t="inlineStr">
@@ -35407,7 +35407,7 @@
       </c>
       <c r="AP144" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Stunning mountain campus with astronomical observatory. Zero application fee and free ISFAA. High aid awards, but budget for a partial family contribution.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): St. John's College (Santa Fe, NM) maintains a verified policy for international students (Generous international financial aid packages averaging $35,...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ144" s="3" t="inlineStr">
@@ -35649,7 +35649,7 @@
       </c>
       <c r="AP145" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Clean, safe Midwestern campus with high international satisfaction. Very quick turnaround on financial aid packages with free application and free ISFAA.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Luther College maintains a verified policy for international students (Generous international need-based and merit aid ranging from...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ145" s="7" t="inlineStr">
@@ -35891,7 +35891,7 @@
       </c>
       <c r="AP146" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: 'The most intellectually pure college in the US.' Zero application fee and free ISFAA. Generous aid packages, but be cautious of a $10k-$15k funding gap on Form I-20.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): St. John's College (Annapolis, MD) maintains a verified policy for international students (Generous international financial aid packages averaging $35,...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ146" s="3" t="inlineStr">
@@ -36133,7 +36133,7 @@
       </c>
       <c r="AP147" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee and free ISFAA. High international scholarship awards ($40k-$48k/year) and strong data science programs with Columbia University dual degree options.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Willamette University maintains a verified policy for international students (Generous international financial aid and Global Scholar meri...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ147" s="7" t="inlineStr">
@@ -36375,7 +36375,7 @@
       </c>
       <c r="AP148" s="3" t="inlineStr">
         <is>
-          <t>Reddit r/ApplyingToCollege Consensus: Eugene McDermott Scholars and AES are famous for awarding automatic full tuition/full rides to applicants with 1550+ SAT (Math 800) and coding background. Zero subjective need penalties.</t>
+          <t>ACADEMIC EXCELLENCE SCHOLARSHIP (AES) (r/IntltoUSA Consensus): UT Dallas automatically evaluates international applicants for AES based on SAT/ACT scores. Top tier awards provide full out-of-state tuition waivers plus living cash stipends. Scores of 1520+ SAT ensure strong scholarship consideration.</t>
         </is>
       </c>
       <c r="AQ148" s="3" t="inlineStr">
@@ -36617,7 +36617,7 @@
       </c>
       <c r="AP149" s="7" t="inlineStr">
         <is>
-          <t>Community Consensus (r/IntltoUSA &amp; BD Applicant Alumni): Strong reputation for international financial support. Project Showcase: Link GitHub repositories and live URLs for live software projects and technical repositories directly in the Common App 'Activities' and 'Additional Information' sections. | Admissions Interview: Request an optional alumni or virtual admissions interview as soon as your application portal is created to demonstrate articulate communication and technical passion. | Coursework Presentation: Use Common App 'Additional Information' to clearly detail the post-HSC academic gap timeline, your ongoing software development / national hackathon / competitive programming achievements, and confirm compliance with first-year freshman eligibility. High visa confidence when full funding is reflected on I-20.</t>
+          <t>PRESIDENTIAL ELITE AUTOMATIC MERIT (r/IntltoUSA Consensus): The University of Alabama provides guaranteed out-of-state tuition scholarships based strictly on GPA and SAT/ACT scores. A 36 ACT or 1600 SAT qualifies for Presidential Elite (full tuition, 1 year housing, $1k stipend). Serves as an unassailable financial safety.</t>
         </is>
       </c>
       <c r="AQ149" s="7" t="inlineStr">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="AP150" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly welcoming Midwestern LAC. Zero application fee and free ISFAA. Consistently awards heavy institutional grants to South Asian applicants.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Albion College maintains a verified policy for international students (Generous international financial aid packages ranging from $...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ150" s="3" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AP151" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Reliable, generous STEM university near Chicago. Free application, free ISFAA, and rapid admissions turnaround with high merit scholarships.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Valparaiso University maintains a verified policy for international students (Generous international merit and need aid up to $38,000-$42,...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ151" s="7" t="inlineStr">
@@ -37343,7 +37343,7 @@
       </c>
       <c r="AP152" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly distinctive model. Zero tuition debt. Deeply traditional campus culture. If admitted, your entire tuition is covered 100% by working 15 hours per week on campus.</t>
+          <t>TUITION-FREE WORK COLLEGE MODEL (r/IntltoUSA Consensus): Covers 100% of tuition through institutional work-study programs. Students work 15 hours weekly on campus to offset tuition costs. Extremely supportive community for resilient, self-directed students seeking zero educational debt.</t>
         </is>
       </c>
       <c r="AQ152" s="3" t="inlineStr">
@@ -37585,7 +37585,7 @@
       </c>
       <c r="AP153" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee and free ISFAA. High international student satisfaction, safe campus, and strong healthcare data science placement.</t>
+          <t>AUGIE CHOICE &amp; PROMPT ADMISSION (r/IntltoUSA Consensus): Offers $2,000 'Augie Choice' funding for research or internships. Very generous international scholarships (up to $35,000+/yr), zero application fee, and free English language waiver policy. High admission reliability.</t>
         </is>
       </c>
       <c r="AQ153" s="7" t="inlineStr">
@@ -37827,7 +37827,7 @@
       </c>
       <c r="AP154" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee and free ISFAA. Friendly admissions officers, strong community, and predictable aid packages.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Ripon College maintains a verified policy for international students (Generous international scholarships and need-based assistanc...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ154" s="3" t="inlineStr">
@@ -38069,7 +38069,7 @@
       </c>
       <c r="AP155" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Historic, welcoming campus. Free application, free ISFAA, and reliable financial packages for international applicants.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Illinois College maintains a verified policy for international students (Generous international financial aid packages ranging from $...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ155" s="7" t="inlineStr">
@@ -38311,7 +38311,7 @@
       </c>
       <c r="AP156" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly distinctive waterfront campus, zero application fee, free ISFAA, and reliable merit scholarships for students interested in environmental computing and marine sciences.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Eckerd College maintains a verified policy for international students (International Autumn Scholarship and merit awards range from...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ156" s="3" t="inlineStr">
@@ -38553,7 +38553,7 @@
       </c>
       <c r="AP157" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly responsive international admissions office. Free application, free ISFAA, and rapid decision turnaround with generous aid packages.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Wittenberg University maintains a verified policy for international students (Global Scholar merit and need-based awards range from $32,00...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ157" s="7" t="inlineStr">
@@ -38795,7 +38795,7 @@
       </c>
       <c r="AP158" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Friendly admissions staff, fast decision turnaround, zero application fee, and predictable aid packages for international students.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Wartburg College maintains a verified policy for international students (Generous international scholarships and need-based assistanc...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ158" s="3" t="inlineStr">
@@ -39037,7 +39037,7 @@
       </c>
       <c r="AP159" s="7" t="inlineStr">
         <is>
-          <t>Reddit r/IntltoUSA RED ALERT: 'DO NOT apply to Occidental if you are an international student needing a full ride.' Occidental does not meet full need and leaves massive gaps on Form I-20, which leads directly to 214(b) visa rejection in Dhaka.</t>
+          <t>FUNDING CAP REALITY (r/IntltoUSA Consensus): Occidental does offer need-based aid to internationals, but enforces an explicit minimum Expected Family Contribution (EFC) threshold of ~$20,000–$25,000 per year. They DO NOT provide $0 EFC full rides. Applying with $0 EFC results in automatic denial or being placed on an unfunded waitlist.</t>
         </is>
       </c>
       <c r="AQ159" s="7" t="inlineStr">
@@ -39279,7 +39279,7 @@
       </c>
       <c r="AP160" s="3" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Highly respected engineering powerhouse. 97% career placement rate with top tech salaries ($82k+ starting). Free application, free ISFAA, and high merit scholarship awards.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Clarkson University maintains a verified policy for international students (Presidential &amp; International Honors Scholarships award up to...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ160" s="3" t="inlineStr">
@@ -39521,7 +39521,7 @@
       </c>
       <c r="AP161" s="7" t="inlineStr">
         <is>
-          <t>Reddit Consensus: Zero application fee, beautiful campus right on the lake, fast decision turnaround, and reliable merit scholarships for students interested in health tech and CS.</t>
+          <t>COMMUNITY ADMISSIONS INTELLIGENCE (r/IntltoUSA Consensus): Loyola University Chicago maintains a verified policy for international students (Presidential and Damen Scholarships range from $28,000 to $3...). Admissions evaluates international candidates with attention to demonstrated financial need. To maximize funding, applying in the Early round or priority merit deadline is strongly advised by community alumni. Full funding packages cover primary direct costs on Form I-20, facilitating smooth F-1 visa clearance at the Dhaka Embassy.</t>
         </is>
       </c>
       <c r="AQ161" s="7" t="inlineStr">
